--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221074</v>
+        <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666979</v>
+        <v>667051</v>
       </c>
       <c r="R2" t="n">
-        <v>7202809</v>
+        <v>7202844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221071</v>
+        <v>125221072</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666946</v>
+        <v>666945</v>
       </c>
       <c r="R3" t="n">
-        <v>7202739</v>
+        <v>7202743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221070</v>
+        <v>125221071</v>
       </c>
       <c r="B5" t="n">
-        <v>92305</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667051</v>
+        <v>666946</v>
       </c>
       <c r="R5" t="n">
-        <v>7202844</v>
+        <v>7202739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125221072</v>
+        <v>125221074</v>
       </c>
       <c r="B6" t="n">
-        <v>78546</v>
+        <v>92287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666945</v>
+        <v>666979</v>
       </c>
       <c r="R6" t="n">
-        <v>7202743</v>
+        <v>7202809</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221070</v>
+        <v>125221074</v>
       </c>
       <c r="B2" t="n">
-        <v>92305</v>
+        <v>92287</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667051</v>
+        <v>666979</v>
       </c>
       <c r="R2" t="n">
-        <v>7202844</v>
+        <v>7202809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221072</v>
+        <v>125221071</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666945</v>
+        <v>666946</v>
       </c>
       <c r="R3" t="n">
-        <v>7202743</v>
+        <v>7202739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221073</v>
+        <v>125221072</v>
       </c>
       <c r="B4" t="n">
-        <v>92285</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666933</v>
+        <v>666945</v>
       </c>
       <c r="R4" t="n">
-        <v>7202749</v>
+        <v>7202743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221071</v>
+        <v>125221070</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>92305</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666946</v>
+        <v>667051</v>
       </c>
       <c r="R5" t="n">
-        <v>7202739</v>
+        <v>7202844</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125221074</v>
+        <v>125221073</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666979</v>
+        <v>666933</v>
       </c>
       <c r="R6" t="n">
-        <v>7202809</v>
+        <v>7202749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221074</v>
+        <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666979</v>
+        <v>667051</v>
       </c>
       <c r="R2" t="n">
-        <v>7202809</v>
+        <v>7202844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221071</v>
+        <v>125221072</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666946</v>
+        <v>666945</v>
       </c>
       <c r="R3" t="n">
-        <v>7202739</v>
+        <v>7202743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221072</v>
+        <v>125221074</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>92287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666945</v>
+        <v>666979</v>
       </c>
       <c r="R4" t="n">
-        <v>7202743</v>
+        <v>7202809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221070</v>
+        <v>125221071</v>
       </c>
       <c r="B5" t="n">
-        <v>92305</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667051</v>
+        <v>666946</v>
       </c>
       <c r="R5" t="n">
-        <v>7202844</v>
+        <v>7202739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221070</v>
+        <v>125221072</v>
       </c>
       <c r="B2" t="n">
-        <v>92305</v>
+        <v>78546</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667051</v>
+        <v>666945</v>
       </c>
       <c r="R2" t="n">
-        <v>7202844</v>
+        <v>7202743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221072</v>
+        <v>125221073</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>92285</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666945</v>
+        <v>666933</v>
       </c>
       <c r="R3" t="n">
-        <v>7202743</v>
+        <v>7202749</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125221073</v>
+        <v>125221070</v>
       </c>
       <c r="B6" t="n">
-        <v>92285</v>
+        <v>92305</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666933</v>
+        <v>667051</v>
       </c>
       <c r="R6" t="n">
-        <v>7202749</v>
+        <v>7202844</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221072</v>
+        <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>92305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666945</v>
+        <v>667051</v>
       </c>
       <c r="R2" t="n">
-        <v>7202743</v>
+        <v>7202844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221073</v>
+        <v>125221071</v>
       </c>
       <c r="B3" t="n">
-        <v>92285</v>
+        <v>78547</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666933</v>
+        <v>666946</v>
       </c>
       <c r="R3" t="n">
-        <v>7202749</v>
+        <v>7202739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221074</v>
+        <v>125221073</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92285</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666979</v>
+        <v>666933</v>
       </c>
       <c r="R4" t="n">
-        <v>7202809</v>
+        <v>7202749</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221071</v>
+        <v>125221072</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666946</v>
+        <v>666945</v>
       </c>
       <c r="R5" t="n">
-        <v>7202739</v>
+        <v>7202743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125221070</v>
+        <v>125221074</v>
       </c>
       <c r="B6" t="n">
-        <v>92305</v>
+        <v>92287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>667051</v>
+        <v>666979</v>
       </c>
       <c r="R6" t="n">
-        <v>7202844</v>
+        <v>7202809</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>92305</v>
+        <v>92460</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221071</v>
+        <v>125221072</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666946</v>
+        <v>666945</v>
       </c>
       <c r="R3" t="n">
-        <v>7202739</v>
+        <v>7202743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221073</v>
+        <v>125221074</v>
       </c>
       <c r="B4" t="n">
-        <v>92285</v>
+        <v>92442</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666933</v>
+        <v>666979</v>
       </c>
       <c r="R4" t="n">
-        <v>7202749</v>
+        <v>7202809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221072</v>
+        <v>125221073</v>
       </c>
       <c r="B5" t="n">
-        <v>78546</v>
+        <v>92440</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666945</v>
+        <v>666933</v>
       </c>
       <c r="R5" t="n">
-        <v>7202743</v>
+        <v>7202749</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125221074</v>
+        <v>125221071</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>78684</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666979</v>
+        <v>666946</v>
       </c>
       <c r="R6" t="n">
-        <v>7202809</v>
+        <v>7202739</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221072</v>
+        <v>125221071</v>
       </c>
       <c r="B3" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666945</v>
+        <v>666946</v>
       </c>
       <c r="R3" t="n">
-        <v>7202743</v>
+        <v>7202739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125221071</v>
+        <v>125221072</v>
       </c>
       <c r="B6" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666946</v>
+        <v>666945</v>
       </c>
       <c r="R6" t="n">
-        <v>7202739</v>
+        <v>7202743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>92522</v>
+        <v>92530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125221074</v>
       </c>
       <c r="B5" t="n">
-        <v>92504</v>
+        <v>92512</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>125221073</v>
       </c>
       <c r="B6" t="n">
-        <v>92502</v>
+        <v>92510</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221070</v>
+        <v>125221072</v>
       </c>
       <c r="B2" t="n">
-        <v>92530</v>
+        <v>78730</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667051</v>
+        <v>666945</v>
       </c>
       <c r="R2" t="n">
-        <v>7202844</v>
+        <v>7202743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221072</v>
+        <v>125221070</v>
       </c>
       <c r="B3" t="n">
-        <v>78726</v>
+        <v>92534</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666945</v>
+        <v>667051</v>
       </c>
       <c r="R3" t="n">
-        <v>7202743</v>
+        <v>7202844</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221071</v>
+        <v>125221074</v>
       </c>
       <c r="B4" t="n">
-        <v>78727</v>
+        <v>92516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666946</v>
+        <v>666979</v>
       </c>
       <c r="R4" t="n">
-        <v>7202739</v>
+        <v>7202809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221074</v>
+        <v>125221071</v>
       </c>
       <c r="B5" t="n">
-        <v>92512</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666979</v>
+        <v>666946</v>
       </c>
       <c r="R5" t="n">
-        <v>7202809</v>
+        <v>7202739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
         <v>125221073</v>
       </c>
       <c r="B6" t="n">
-        <v>92510</v>
+        <v>92514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221074</v>
+        <v>125221071</v>
       </c>
       <c r="B4" t="n">
-        <v>92516</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666979</v>
+        <v>666946</v>
       </c>
       <c r="R4" t="n">
-        <v>7202809</v>
+        <v>7202739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221071</v>
+        <v>125221074</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>92516</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666946</v>
+        <v>666979</v>
       </c>
       <c r="R5" t="n">
-        <v>7202739</v>
+        <v>7202809</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221071</v>
+        <v>125221074</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>92516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666946</v>
+        <v>666979</v>
       </c>
       <c r="R4" t="n">
-        <v>7202739</v>
+        <v>7202809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221074</v>
+        <v>125221071</v>
       </c>
       <c r="B5" t="n">
-        <v>92516</v>
+        <v>78731</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666979</v>
+        <v>666946</v>
       </c>
       <c r="R5" t="n">
-        <v>7202809</v>
+        <v>7202739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221072</v>
+        <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>78730</v>
+        <v>92536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666945</v>
+        <v>667051</v>
       </c>
       <c r="R2" t="n">
-        <v>7202743</v>
+        <v>7202844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221070</v>
+        <v>125221072</v>
       </c>
       <c r="B3" t="n">
-        <v>92534</v>
+        <v>78731</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667051</v>
+        <v>666945</v>
       </c>
       <c r="R3" t="n">
-        <v>7202844</v>
+        <v>7202743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>125221074</v>
       </c>
       <c r="B4" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125221071</v>
       </c>
       <c r="B5" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>125221073</v>
       </c>
       <c r="B6" t="n">
-        <v>92514</v>
+        <v>92516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221070</v>
+        <v>125221072</v>
       </c>
       <c r="B2" t="n">
-        <v>92536</v>
+        <v>78731</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667051</v>
+        <v>666945</v>
       </c>
       <c r="R2" t="n">
-        <v>7202844</v>
+        <v>7202743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221072</v>
+        <v>125221070</v>
       </c>
       <c r="B3" t="n">
-        <v>78731</v>
+        <v>92536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666945</v>
+        <v>667051</v>
       </c>
       <c r="R3" t="n">
-        <v>7202743</v>
+        <v>7202844</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221074</v>
+        <v>125221071</v>
       </c>
       <c r="B4" t="n">
-        <v>92518</v>
+        <v>78732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666979</v>
+        <v>666946</v>
       </c>
       <c r="R4" t="n">
-        <v>7202809</v>
+        <v>7202739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221071</v>
+        <v>125221074</v>
       </c>
       <c r="B5" t="n">
-        <v>78732</v>
+        <v>92518</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666946</v>
+        <v>666979</v>
       </c>
       <c r="R5" t="n">
-        <v>7202739</v>
+        <v>7202809</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>125221070</v>
       </c>
       <c r="B3" t="n">
-        <v>92536</v>
+        <v>92538</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125221074</v>
       </c>
       <c r="B5" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>125221073</v>
       </c>
       <c r="B6" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>125221070</v>
       </c>
       <c r="B3" t="n">
-        <v>92538</v>
+        <v>92540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125221074</v>
       </c>
       <c r="B5" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>125221073</v>
       </c>
       <c r="B6" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221072</v>
+        <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>78731</v>
+        <v>92544</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666945</v>
+        <v>667051</v>
       </c>
       <c r="R2" t="n">
-        <v>7202743</v>
+        <v>7202844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221070</v>
+        <v>125221072</v>
       </c>
       <c r="B3" t="n">
-        <v>92540</v>
+        <v>78735</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667051</v>
+        <v>666945</v>
       </c>
       <c r="R3" t="n">
-        <v>7202844</v>
+        <v>7202743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>125221071</v>
       </c>
       <c r="B4" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>125221074</v>
       </c>
       <c r="B5" t="n">
-        <v>92522</v>
+        <v>92526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>125221073</v>
       </c>
       <c r="B6" t="n">
-        <v>92520</v>
+        <v>92524</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>92544</v>
+        <v>92547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221072</v>
       </c>
       <c r="B3" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221071</v>
+        <v>125221074</v>
       </c>
       <c r="B4" t="n">
-        <v>78736</v>
+        <v>92529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666946</v>
+        <v>666979</v>
       </c>
       <c r="R4" t="n">
-        <v>7202739</v>
+        <v>7202809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221074</v>
+        <v>125221071</v>
       </c>
       <c r="B5" t="n">
-        <v>92526</v>
+        <v>78739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666979</v>
+        <v>666946</v>
       </c>
       <c r="R5" t="n">
-        <v>7202809</v>
+        <v>7202739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
         <v>125221073</v>
       </c>
       <c r="B6" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221070</v>
+        <v>125221072</v>
       </c>
       <c r="B2" t="n">
-        <v>92547</v>
+        <v>78738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667051</v>
+        <v>666945</v>
       </c>
       <c r="R2" t="n">
-        <v>7202844</v>
+        <v>7202743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221072</v>
+        <v>125221070</v>
       </c>
       <c r="B3" t="n">
-        <v>78738</v>
+        <v>92547</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666945</v>
+        <v>667051</v>
       </c>
       <c r="R3" t="n">
-        <v>7202743</v>
+        <v>7202844</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221074</v>
+        <v>125221071</v>
       </c>
       <c r="B4" t="n">
-        <v>92529</v>
+        <v>78739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666979</v>
+        <v>666946</v>
       </c>
       <c r="R4" t="n">
-        <v>7202809</v>
+        <v>7202739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221071</v>
+        <v>125221074</v>
       </c>
       <c r="B5" t="n">
-        <v>78739</v>
+        <v>92529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666946</v>
+        <v>666979</v>
       </c>
       <c r="R5" t="n">
-        <v>7202739</v>
+        <v>7202809</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 21509-2025 artfynd.xlsx
+++ b/artfynd/A 21509-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221072</v>
+        <v>125221070</v>
       </c>
       <c r="B2" t="n">
-        <v>78738</v>
+        <v>92547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666945</v>
+        <v>667051</v>
       </c>
       <c r="R2" t="n">
-        <v>7202743</v>
+        <v>7202844</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221070</v>
+        <v>125221072</v>
       </c>
       <c r="B3" t="n">
-        <v>92547</v>
+        <v>78738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>667051</v>
+        <v>666945</v>
       </c>
       <c r="R3" t="n">
-        <v>7202844</v>
+        <v>7202743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221071</v>
+        <v>125221074</v>
       </c>
       <c r="B4" t="n">
-        <v>78739</v>
+        <v>92529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666946</v>
+        <v>666979</v>
       </c>
       <c r="R4" t="n">
-        <v>7202739</v>
+        <v>7202809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125221074</v>
+        <v>125221071</v>
       </c>
       <c r="B5" t="n">
-        <v>92529</v>
+        <v>78739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666979</v>
+        <v>666946</v>
       </c>
       <c r="R5" t="n">
-        <v>7202809</v>
+        <v>7202739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
